--- a/outputs/resultats/td/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/td/2025_t4_vs_2024_t4/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'DURÉE CONTRACTUELLE RESTANTE', et des notes ont été ajoutées et modifiées concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une réorganisation des informations présentées dans le tableau, ce qui peut affecter la transparence et la comparabilité des données financières. La suppression de l'indicateur et les modifications des notes peuvent refléter un changement dans la manière dont la banque gère ou présente ses engagements financiers, ce qui est crucial pour les analystes et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des engagements financiers de la banque et leur conformité aux normes de divulgation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant l'indicateur 'Engagements de clients au titre d’acceptations' et en ajoutant des notes sur les obligations sécurisées, tout en modifiant les montants des engagements de crédit. Pertinence métier : Ce changement met en évidence une révision significative de la présentation des engagements financiers de la banque, ce qui peut affecter la transparence et la compréhension des risques associés aux obligations sécurisées et aux engagements de crédit. La suppression de certains indicateurs et l'ajout de nouvelles notes peuvent influencer la perception des risques de liquidité et de crédit par les parties prenantes, en particulier si les montants en jeu sont substantiels. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et de crédit, ainsi que sur la comparabilité des rapports financiers de TD avec ceux de ses pairs.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -594,55 +594,59 @@
       <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Évolution future des fonds propres réglementaires</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Billets avec remboursement de capital à recours limité – série 6' et 'Évolution future des fonds propres réglementaires'. Suppression de la note sur le rachat des actions privilégiées. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure des fonds propres réglementaires de la banque, en introduisant de nouveaux instruments financiers et en supprimant des actions privilégiées. Cela reflète une stratégie potentielle de gestion du capital qui pourrait affecter la composition des fonds propres réglementaires et la capacité de la banque à répondre aux exigences prudentielles. Point de surveillance : Surveiller l'impact de ces nouveaux instruments sur les ratios de fonds propres réglementaires et la stratégie de capitalisation de la banque.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent 75 milliards de dollars d’obligations sécurisées dont une tranche de 2 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 18 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 37 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>⁵ Comprennent 70 milliards de dollars d’obligations sécurisées dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 4 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 24 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 19 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et 'Participation dans Schwab', et en ajustant les notes de bas de tableau concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une révision de la présentation des engagements et des participations, ce qui peut affecter la transparence et la compréhension des risques associés à ces éléments. La suppression des indicateurs pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ces engagements, tandis que les ajustements des notes de bas de tableau reflètent des modifications dans les montants des obligations sécurisées et des engagements de crédit. Cela pourrait avoir un impact sur la perception des risques de liquidité et de crédit par les parties prenantes. Point de surveillance : Surveiller l'impact de ces modifications sur la transparence des risques et la comparabilité avec les rapports précédents.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -652,38 +656,42 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent 609 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Trésorerie et montants à recevoir de banques</t>
+          <t>⁶ Comprennent 623 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : Le tableau 'ACTIFS GREVÉS ET ACTIFS NON GREVÉS' a été modifié avec l'ajout de l'indicateur 'Trésorerie et montants à recevoir de banques' et la suppression de 'Trésorerie et montants à recevoir'. De plus, une note a été supprimée et une autre modifiée. Pertinence métier : Ce changement met en évidence une réorganisation des indicateurs financiers dans le tableau, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement influencer l'analyse de la liquidité et de la gestion des actifs de la banque. La suppression de la note sur le retraitement des soldes pourrait également avoir des implications sur la transparence des informations fournies. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des actifs grevés et non grevés, ainsi que sur la transparence des informations financières fournies par la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et 'Participation dans Schwab', et en ajustant les notes de bas de tableau concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une révision de la présentation des engagements et des participations, ce qui peut affecter la transparence et la compréhension des risques associés à ces éléments. La suppression des indicateurs pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ces engagements, tandis que les ajustements des notes de bas de tableau reflètent des modifications dans les montants des obligations sécurisées et des engagements de crédit. Cela pourrait avoir un impact sur la perception des risques de liquidité et de crédit par les parties prenantes. Point de surveillance : Surveiller l'impact de ces modifications sur la transparence des risques et la comparabilité avec les rapports précédents.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -703,42 +711,38 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Les autres actifs comprennent la participation dans Schwab, le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Les autres actifs comprennent le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
-        </is>
-      </c>
+          <t>Engagements de clients au titre d’acceptations</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : Le tableau 'ACTIFS GREVÉS ET ACTIFS NON GREVÉS' a été modifié avec l'ajout de l'indicateur 'Trésorerie et montants à recevoir de banques' et la suppression de 'Trésorerie et montants à recevoir'. De plus, une note a été supprimée et une autre modifiée. Pertinence métier : Ce changement met en évidence une réorganisation des indicateurs financiers dans le tableau, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement influencer l'analyse de la liquidité et de la gestion des actifs de la banque. La suppression de la note sur le retraitement des soldes pourrait également avoir des implications sur la transparence des informations fournies. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des actifs grevés et non grevés, ainsi que sur la transparence des informations financières fournies par la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et 'Participation dans Schwab', et en ajustant les notes de bas de tableau concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une révision de la présentation des engagements et des participations, ce qui peut affecter la transparence et la compréhension des risques associés à ces éléments. La suppression des indicateurs pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ces engagements, tandis que les ajustements des notes de bas de tableau reflètent des modifications dans les montants des obligations sécurisées et des engagements de crédit. Cela pourrait avoir un impact sur la perception des risques de liquidité et de crédit par les parties prenantes. Point de surveillance : Surveiller l'impact de ces modifications sur la transparence des risques et la comparabilité avec les rapports précédents.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -758,17 +762,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -783,13 +787,13 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Trésorerie et montants à recevoir</t>
+          <t>Participation dans Schwab</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : Le tableau 'ACTIFS GREVÉS ET ACTIFS NON GREVÉS' a été modifié avec l'ajout de l'indicateur 'Trésorerie et montants à recevoir de banques' et la suppression de 'Trésorerie et montants à recevoir'. De plus, une note a été supprimée et une autre modifiée. Pertinence métier : Ce changement met en évidence une réorganisation des indicateurs financiers dans le tableau, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement influencer l'analyse de la liquidité et de la gestion des actifs de la banque. La suppression de la note sur le retraitement des soldes pourrait également avoir des implications sur la transparence des informations fournies. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des actifs grevés et non grevés, ainsi que sur la transparence des informations financières fournies par la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et 'Participation dans Schwab', et en ajustant les notes de bas de tableau concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une révision de la présentation des engagements et des participations, ce qui peut affecter la transparence et la compréhension des risques associés à ces éléments. La suppression des indicateurs pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ces engagements, tandis que les ajustements des notes de bas de tableau reflètent des modifications dans les montants des obligations sécurisées et des engagements de crédit. Cela pourrait avoir un impact sur la perception des risques de liquidité et de crédit par les parties prenantes. Point de surveillance : Surveiller l'impact de ces modifications sur la transparence des risques et la comparabilité avec les rapports précédents.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -809,19 +813,19 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
@@ -829,27 +833,23 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Comprennent 75 milliards de dollars d’obligations sécurisées dont une tranche de 2 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 18 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 37 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 70 milliards de dollars d’obligations sécurisées dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 4 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 24 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 19 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
-        </is>
-      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Variation chiffrée propre Ce qui change : Les montants des obligations sécurisées et des engagements de crédit ont été ajustés de 75 milliards à 70 milliards et de 609 millions à 623 millions respectivement. Pertinence métier : Ce changement ne modifie pas la substance de la divulgation réglementaire ou de gestion des risques. Il s'agit de variations chiffrées propres à la banque, sans impact sur les seuils ou exigences réglementaires. Point de surveillance : Aucun point de surveillance requis car il s'agit de variations chiffrées internes sans implication réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant l'indicateur 'Engagements de clients au titre d’acceptations' et en ajoutant des notes sur les obligations sécurisées, tout en modifiant les montants des engagements de crédit. Pertinence métier : Ce changement met en évidence une révision significative de la présentation des engagements financiers de la banque, ce qui peut affecter la transparence et la compréhension des risques associés aux obligations sécurisées et aux engagements de crédit. La suppression de certains indicateurs et l'ajout de nouvelles notes peuvent influencer la perception des risques de liquidité et de crédit par les parties prenantes, en particulier si les montants en jeu sont substantiels. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et de crédit, ainsi que sur la comparabilité des rapports financiers de TD avec ceux de ses pairs.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
@@ -864,19 +864,19 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
@@ -889,22 +889,22 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>Comprennent 54 milliards de dollars d’obligations sécurisées dont une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 1 milliard de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 12 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 31 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 4 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Comprennent 609 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 623 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Variation chiffrée propre Ce qui change : Les montants des obligations sécurisées et des engagements de crédit ont été ajustés de 75 milliards à 70 milliards et de 609 millions à 623 millions respectivement. Pertinence métier : Ce changement ne modifie pas la substance de la divulgation réglementaire ou de gestion des risques. Il s'agit de variations chiffrées propres à la banque, sans impact sur les seuils ou exigences réglementaires. Point de surveillance : Aucun point de surveillance requis car il s'agit de variations chiffrées internes sans implication réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant l'indicateur 'Engagements de clients au titre d’acceptations' et en ajoutant des notes sur les obligations sécurisées, tout en modifiant les montants des engagements de crédit. Pertinence métier : Ce changement met en évidence une révision significative de la présentation des engagements financiers de la banque, ce qui peut affecter la transparence et la compréhension des risques associés aux obligations sécurisées et aux engagements de crédit. La suppression de certains indicateurs et l'ajout de nouvelles notes peuvent influencer la perception des risques de liquidité et de crédit par les parties prenantes, en particulier si les montants en jeu sont substantiels. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et de crédit, ainsi que sur la comparabilité des rapports financiers de TD avec ceux de ses pairs.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
@@ -919,17 +919,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -950,12 +950,12 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Variation chiffrée propre Ce qui change : Les montants des obligations sécurisées et des engagements de crédit ont été ajustés de 75 milliards à 70 milliards et de 609 millions à 623 millions respectivement. Pertinence métier : Ce changement ne modifie pas la substance de la divulgation réglementaire ou de gestion des risques. Il s'agit de variations chiffrées propres à la banque, sans impact sur les seuils ou exigences réglementaires. Point de surveillance : Aucun point de surveillance requis car il s'agit de variations chiffrées internes sans implication réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant l'indicateur 'Engagements de clients au titre d’acceptations' et en ajoutant des notes sur les obligations sécurisées, tout en modifiant les montants des engagements de crédit. Pertinence métier : Ce changement met en évidence une révision significative de la présentation des engagements financiers de la banque, ce qui peut affecter la transparence et la compréhension des risques associés aux obligations sécurisées et aux engagements de crédit. La suppression de certains indicateurs et l'ajout de nouvelles notes peuvent influencer la perception des risques de liquidité et de crédit par les parties prenantes, en particulier si les montants en jeu sont substantiels. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et de crédit, ainsi que sur la comparabilité des rapports financiers de TD avec ceux de ses pairs.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -990,18 +990,18 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 75 milliards de dollars d’obligations sécurisées dont une tranche de 2 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 18 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 37 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent 573 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'DURÉE CONTRACTUELLE RESTANTE', et des notes ont été ajoutées et modifiées concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une réorganisation des informations présentées dans le tableau, ce qui peut affecter la transparence et la comparabilité des données financières. La suppression de l'indicateur et les modifications des notes peuvent refléter un changement dans la manière dont la banque gère ou présente ses engagements financiers, ce qui est crucial pour les analystes et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des engagements financiers de la banque et leur conformité aux normes de divulgation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'DURÉE CONTRACTUELLE RESTANTE' en supprimant l'indicateur 'Engagements de clients au titre d’acceptations' et en ajoutant des notes sur les obligations sécurisées, tout en modifiant les montants des engagements de crédit. Pertinence métier : Ce changement met en évidence une révision significative de la présentation des engagements financiers de la banque, ce qui peut affecter la transparence et la compréhension des risques associés aux obligations sécurisées et aux engagements de crédit. La suppression de certains indicateurs et l'ajout de nouvelles notes peuvent influencer la perception des risques de liquidité et de crédit par les parties prenantes, en particulier si les montants en jeu sont substantiels. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et de crédit, ainsi que sur la comparabilité des rapports financiers de TD avec ceux de ses pairs.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1021,47 +1021,47 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
+          <t>EXPOSITIONS BRUTES AU RISQUE DE CRÉDIT – Approche standard et approches fondées sur les notations internes (NI)¹</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Renommage</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 54 milliards de dollars d’obligations sécurisées dont une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 1 milliard de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 12 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 31 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 4 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+          <t>Total – expositions de détail</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 609 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+          <t>Total – risque de crédit de détail</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'DURÉE CONTRACTUELLE RESTANTE', et des notes ont été ajoutées et modifiées concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une réorganisation des informations présentées dans le tableau, ce qui peut affecter la transparence et la comparabilité des données financières. La suppression de l'indicateur et les modifications des notes peuvent refléter un changement dans la manière dont la banque gère ou présente ses engagements financiers, ce qui est crucial pour les analystes et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des engagements financiers de la banque et leur conformité aux normes de divulgation.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Renommage d'indicateur Ce qui change : TD renomme un indicateur dans le tableau des expositions brutes au risque de crédit, passant de 'Total – expositions de détail' à 'Total – risque de crédit de détail'. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il ne modifie ni la méthodologie ni les indicateurs de risque, et n'a pas d'impact sur la gouvernance ou la conformité réglementaire. Il s'agit simplement d'une reformulation qui n'introduit pas de nouvelle information ou de changement de posture. Point de surveillance : Aucun point de surveillance requis, car le changement est non substantif et n'affecte pas la gestion des risques ou la transparence réglementaire.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
+          <t>FINANCEMENT DE GROS</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1096,18 +1096,18 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Engagements de clients au titre d’acceptations</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Dont : Total</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'DURÉE CONTRACTUELLE RESTANTE', et des notes ont été ajoutées et modifiées concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une réorganisation des informations présentées dans le tableau, ce qui peut affecter la transparence et la comparabilité des données financières. La suppression de l'indicateur et les modifications des notes peuvent refléter un changement dans la manière dont la banque gère ou présente ses engagements financiers, ce qui est crucial pour les analystes et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des engagements financiers de la banque et leur conformité aux normes de divulgation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
+          <t>FINANCEMENT DE GROS</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1147,18 +1147,22 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 573 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>Exclut les acceptations bancaires, lesquelles sont présentées dans le tableau « Durée contractuelle restante » figurant à la section « Gestion des risques » du présent document.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>¹ Comprennent seulement les dépôts commerciaux à échéance déterminée auprès de banques.</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'DURÉE CONTRACTUELLE RESTANTE', et des notes ont été ajoutées et modifiées concernant les obligations sécurisées et les engagements de crédit. Pertinence métier : Ce changement met en évidence une réorganisation des informations présentées dans le tableau, ce qui peut affecter la transparence et la comparabilité des données financières. La suppression de l'indicateur et les modifications des notes peuvent refléter un changement dans la manière dont la banque gère ou présente ses engagements financiers, ce qui est crucial pour les analystes et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des engagements financiers de la banque et leur conformité aux normes de divulgation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1178,47 +1182,47 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>EXPOSITIONS BRUTES AU RISQUE DE CRÉDIT – Approche standard et approches fondées sur les notations internes (NI)¹</t>
+          <t>FINANCEMENT DE GROS</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Renommage</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Total – expositions de détail</t>
+          <t>La présentation a été modifiée pour n’inclure que les dépôts commerciaux à échéance déterminée auprès de banques, afin de mieux harmoniser l’information avec la façon dont la direction perçoit la composition du financement de gros de la Banque.</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Total – risque de crédit de détail</t>
+          <t>² Comprennent les titres adossés à des créances hypothécaires émises à des investisseurs externes et dans le cadre des activités de négociation de prêts hypothécaires résidentiels du secteur Services bancaires de gros.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Renommage d'indicateur Ce qui change : L'indicateur 'Total – expositions de détail' a été renommé en 'Total – risque de crédit de détail'. Pertinence métier : Ce changement est une reformulation sans impact substantiel sur la divulgation ou la méthodologie. Il ne modifie pas la substance de l'information fournie, mais ajuste simplement le libellé pour une meilleure clarté ou précision. Point de surveillance : Aucun point de surveillance particulier n'est requis, car il s'agit d'une reformulation sans impact sur la gestion des risques ou la conformité réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
@@ -1253,18 +1257,22 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires émises à des investisseurs externes et dans le cadre des activités de négociation de prêts hypothécaires résidentiels du secteur Services bancaires de gros.</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,3 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
+          <t>³ Comprennent a) la dette de premier rang émise avant le 23 septembre 2018; et b) la dette de premier rang émise à partir du 23 septembre 2018 qui est exclue du régime de recapitalisation interne des banques, y compris la dette dont la durée initiale est de moins de 400 jours.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1304,18 +1312,22 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent a) la dette de premier rang émise avant le 23 septembre 2018; et b) la dette de premier rang émise à partir du 23 septembre 2018 qui est exclue du régime de recapitalisation interne des banques, y compris la dette dont la durée initiale est de moins de 400 jours.</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 26,9 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+          <t>⁴ Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,3 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1360,17 +1372,17 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Exclut les acceptations bancaires, lesquelles sont présentées dans le tableau « Durée contractuelle restante » figurant à la section « Gestion des risques » du présent document.</t>
+          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 4,4 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (5,7 milliards de dollars au 31 octobre 2023).</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Comprennent seulement les dépôts commerciaux à échéance déterminée auprès de banques.</t>
+          <t>⁵ Les billets et débentures subordonnés ne sont pas considérés en tant que financement de gros étant donné qu’ils peuvent être engagés essentiellement à des fins de gestion des fonds propres.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1410,18 +1422,22 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 4,4 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (5,7 milliards de dollars au 31 octobre 2023).</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+          <t>Les billets et débentures subordonnés ne sont pas considérés en tant que financement de gros étant donné qu’ils peuvent être engagés essentiellement à des fins de gestion des fonds propres.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>⁶ Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 26,9 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1472,7 +1488,7 @@
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : TD modifie le tableau « FINANCEMENT DE GROS » en ajoutant un indicateur « Dont : Total » et en modifiant plusieurs notes explicatives. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des informations sur le financement de gros, ce qui peut affecter la transparence et la compréhension des sources de financement de la banque. L'ajout de l'indicateur « Dont : Total » et la modification des notes explicatives peuvent influencer la perception des risques de liquidité et de financement par les investisseurs et les régulateurs. Cela pourrait également avoir un impact sur la comparabilité des données avec celles des pairs du secteur. Point de surveillance : Surveiller l'impact de ces modifications sur l'évaluation des risques de liquidité et la transparence des rapports financiers de TD.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1522,12 +1538,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Le tableau comprend les billets garantis et non garantis, de premier rang et subordonnés, sauf les billets structurés et le papier commercial, émis à des investisseurs externes et d’une durée initiale de plus de un an.</t>
+          <t>Le tableau comprend les billets garantis et non garantis, de premier rang et subordonnés, sauf les billets structurés et le papier commercial, émis à des investisseurs externes et d’une durée initiale de plus d’un an.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité Ce qui change : La note de bas de tableau a été modifiée pour inclure une distinction entre les billets garantis et non garantis, ainsi que de premier rang et subordonnés. Pertinence métier : Ce changement met en évidence une clarification importante dans la présentation du financement à long terme, ce qui peut affecter la perception de la liquidité et de la structure de financement de la banque. La distinction entre les types de billets est cruciale pour évaluer le risque de liquidité et la qualité du financement. Point de surveillance : Surveiller comment cette nouvelle distinction impacte l'analyse de la liquidité et la stratégie de financement de la banque, ainsi que sa conformité aux attentes réglementaires en matière de divulgation de la liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie la composition du tableau de financement à long terme pour inclure les billets garantis et non garantis, de premier rang et subordonnés. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement à long terme de la banque, ce qui peut affecter la perception de sa structure de financement et de sa liquidité. En incluant des détails sur les billets garantis et non garantis, de premier rang et subordonnés, TD améliore la transparence et la compréhension des investisseurs sur la qualité et la sécurité de ses instruments de financement. Cela peut également influencer l'évaluation des risques de liquidité par les régulateurs et les analystes, en fournissant une vue plus complète des engagements financiers de la banque. Point de surveillance : Surveiller l'impact de cette modification sur l'évaluation des risques de liquidité et la perception des investisseurs quant à la solidité financière de TD.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1578,7 +1594,7 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'LIENS ENTRE LE RISQUE DE MARCHÉ ET LE BILAN', ainsi que la note associée concernant le retraitement des soldes pour IFRS 17. Pertinence métier : Ce changement met en évidence une modification structurelle du rapport de gestion des risques, ce qui peut affecter la transparence et la comparabilité des informations sur le risque de marché. La suppression de l'indicateur et de la note pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ses engagements liés aux acceptations, potentiellement en lien avec l'adoption d'IFRS 17. Point de surveillance : Surveiller l'impact de la suppression de cet indicateur sur la compréhension des risques de marché et la conformité aux normes IFRS 17.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'LIENS ENTRE LE RISQUE DE MARCHÉ ET LE BILAN' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et les notes associées à l'adoption d'IFRS 17. Pertinence métier : Ce changement met en évidence une révision de la manière dont TD présente les liens entre le risque de marché et le bilan, ce qui pourrait affecter la transparence et la compréhension des engagements de clients. La suppression des notes sur IFRS 17 pourrait également réduire la clarté sur l'impact de cette norme comptable sur les résultats financiers. Cela pourrait influencer la perception des risques de marché par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette modification sur la transparence des divulgations de risque de marché et l'alignement avec les normes comptables IFRS.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1629,7 +1645,7 @@
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Engagements de clients au titre d’acceptations' a été supprimé du tableau 'LIENS ENTRE LE RISQUE DE MARCHÉ ET LE BILAN', ainsi que la note associée concernant le retraitement des soldes pour IFRS 17. Pertinence métier : Ce changement met en évidence une modification structurelle du rapport de gestion des risques, ce qui peut affecter la transparence et la comparabilité des informations sur le risque de marché. La suppression de l'indicateur et de la note pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ses engagements liés aux acceptations, potentiellement en lien avec l'adoption d'IFRS 17. Point de surveillance : Surveiller l'impact de la suppression de cet indicateur sur la compréhension des risques de marché et la conformité aux normes IFRS 17.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : TD modifie le tableau 'LIENS ENTRE LE RISQUE DE MARCHÉ ET LE BILAN' en supprimant les indicateurs 'Engagements de clients au titre d’acceptations' et les notes associées à l'adoption d'IFRS 17. Pertinence métier : Ce changement met en évidence une révision de la manière dont TD présente les liens entre le risque de marché et le bilan, ce qui pourrait affecter la transparence et la compréhension des engagements de clients. La suppression des notes sur IFRS 17 pourrait également réduire la clarté sur l'impact de cette norme comptable sur les résultats financiers. Cela pourrait influencer la perception des risques de marché par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette modification sur la transparence des divulgations de risque de marché et l'alignement avec les normes comptables IFRS.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1649,38 +1665,38 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
+          <t>MESURES DU RISQUE DE MARCHÉ DU PORTEFEUILLE</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>À compter du 31 juillet 2025, les mesures de sensibilité sont présentées par devise afin de mettre en évidence la sensibilité des produits d’intérêts nets aux variations des taux sous-jacents.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Risque de marché (autre que de négociation) structurel</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : Les notes du tableau sur la sensibilité au risque de taux d'intérêt structurel ont été modifiées pour inclure des précisions sur la présentation par devise et l'exclusion des expositions du secteur Services bancaires de gros. Pertinence métier : Ce changement met en évidence une approche plus détaillée et segmentée de la gestion du risque de taux d'intérêt, en alignement avec les attentes de transparence et de précision dans les rapports financiers. La présentation par devise permet une meilleure compréhension des expositions spécifiques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette segmentation sur la gestion des risques et la communication financière, ainsi que l'adaptation des systèmes de reporting pour intégrer ces nouvelles exigences.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : TD supprime l'indicateur 'Risque de marché (autre que de négociation) structurel' du tableau des mesures du risque de marché du portefeuille. Pertinence métier : Ce changement met en évidence une modification dans la manière dont TD évalue et présente ses risques de marché. La suppression de cet indicateur pourrait indiquer un changement dans la perception ou la gestion de ce type de risque, ce qui peut affecter la transparence et la comparabilité des risques de marché avec d'autres institutions financières. Cela pourrait également signaler une réévaluation des priorités ou des méthodologies de gestion des risques de marché par la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la divulgation des risques de marché et évaluer si d'autres indicateurs ou méthodologies compensent cette absence.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1700,17 +1716,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
+          <t>RATIO DE LIQUIDITÉ À LONG TERME¹</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>121</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1720,18 +1736,22 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>⁴</t>
+        </is>
+      </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt et peut comprendre des ajustements au titre d’éléments non récurrents.</t>
+          <t>Certains éléments de l’actif et du passif réputés interdépendants par le BSIF, et à ce titre, leurs coefficients de FSR et de FSD sont ajustés à zéro. Les passifs interdépendants ne peuvent être échus pendant que l’actif demeure au bilan, ne peuvent servir à financer d’autres actifs tandis que le principal de l’actif ne peut servir qu’à rembourser le passif. Par conséquent, les seuls actifs et passifs interdépendants de la Banque qui sont admissibles à ce traitement sont les passifs découlant du Programme des Obligations hypothécaires du Canada et leurs actifs non grevés correspondants.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : Les notes du tableau sur la sensibilité au risque de taux d'intérêt structurel ont été modifiées pour inclure des précisions sur la présentation par devise et l'exclusion des expositions du secteur Services bancaires de gros. Pertinence métier : Ce changement met en évidence une approche plus détaillée et segmentée de la gestion du risque de taux d'intérêt, en alignement avec les attentes de transparence et de précision dans les rapports financiers. La présentation par devise permet une meilleure compréhension des expositions spécifiques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette segmentation sur la gestion des risques et la communication financière, ainsi que l'adaptation des systèmes de reporting pour intégrer ces nouvelles exigences.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires ou conformité Ce qui change : TD modifie la note de bas de tableau concernant le ratio de liquidité à long terme pour inclure des éléments de l'actif et du passif réputés interdépendants par le BSIF. Pertinence métier : Ce changement met en évidence une clarification importante concernant la gestion de la liquidité à long terme de la banque, en précisant les éléments de l'actif et du passif qui sont considérés comme interdépendants selon les directives du BSIF. Cela peut avoir un impact sur la manière dont la banque gère ses ressources financières et respecte les exigences réglementaires en matière de liquidité. Cette modification améliore la transparence et la conformité aux normes prudentielles, ce qui est crucial pour maintenir la confiance des investisseurs et des régulateurs. Point de surveillance : Surveiller l'impact de cette clarification sur les pratiques de gestion de la liquidité de TD et son alignement avec les attentes du BSIF.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1771,22 +1791,18 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>N’inclut pas les expositions du secteur Services bancaires de gros.</t>
+          <t>À compter du 31 juillet 2025, les mesures de sensibilité sont présentées par devise afin de mettre en évidence la sensibilité des produits d’intérêts nets aux variations des taux sous-jacents.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : Les notes du tableau sur la sensibilité au risque de taux d'intérêt structurel ont été modifiées pour inclure des précisions sur la présentation par devise et l'exclusion des expositions du secteur Services bancaires de gros. Pertinence métier : Ce changement met en évidence une approche plus détaillée et segmentée de la gestion du risque de taux d'intérêt, en alignement avec les attentes de transparence et de précision dans les rapports financiers. La présentation par devise permet une meilleure compréhension des expositions spécifiques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette segmentation sur la gestion des risques et la communication financière, ainsi que l'adaptation des systèmes de reporting pour intégrer ces nouvelles exigences.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Hypothèses ou explications de risque Ce qui change : TD modifie la présentation des mesures de sensibilité au risque de taux d'intérêt structurel en ajoutant des notes qui précisent que les mesures seront présentées par devise à partir du 31 juillet 2025 et en modifiant la description des expositions incluses. Pertinence métier : Ce changement met en évidence une approche plus détaillée et granulaire de la gestion du risque de taux d'intérêt en introduisant une présentation par devise. Cela améliore la transparence et permet une meilleure évaluation des risques associés aux fluctuations des taux d'intérêt dans différentes devises. La modification de la note pour exclure les expositions du secteur Services bancaires de gros clarifie également la portée des mesures de sensibilité, ce qui est crucial pour une évaluation précise des risques. Point de surveillance : Surveiller l'impact de cette nouvelle granularité sur la gestion des risques de taux d'intérêt et la manière dont elle pourrait influencer les décisions stratégiques de couverture de la banque.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1806,22 +1822,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
+          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1832,12 +1848,12 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Autres titres de créance</t>
+          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt et peut comprendre des ajustements au titre d’éléments non récurrents.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Hypothèses ou explications de risque Ce qui change : TD modifie la présentation des mesures de sensibilité au risque de taux d'intérêt structurel en ajoutant des notes qui précisent que les mesures seront présentées par devise à partir du 31 juillet 2025 et en modifiant la description des expositions incluses. Pertinence métier : Ce changement met en évidence une approche plus détaillée et granulaire de la gestion du risque de taux d'intérêt en introduisant une présentation par devise. Cela améliore la transparence et permet une meilleure évaluation des risques associés aux fluctuations des taux d'intérêt dans différentes devises. La modification de la note pour exclure les expositions du secteur Services bancaires de gros clarifie également la portée des mesures de sensibilité, ce qui est crucial pour une évaluation précise des risques. Point de surveillance : Surveiller l'impact de cette nouvelle granularité sur la gestion des risques de taux d'intérêt et la manière dont elle pourrait influencer les décisions stratégiques de couverture de la banque.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1857,22 +1873,22 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
+          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1883,12 +1899,12 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Autres titres</t>
+          <t>Comprend les expositions aux autres devises.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Hypothèses ou explications de risque Ce qui change : TD modifie la présentation des mesures de sensibilité au risque de taux d'intérêt structurel en ajoutant des notes qui précisent que les mesures seront présentées par devise à partir du 31 juillet 2025 et en modifiant la description des expositions incluses. Pertinence métier : Ce changement met en évidence une approche plus détaillée et granulaire de la gestion du risque de taux d'intérêt en introduisant une présentation par devise. Cela améliore la transparence et permet une meilleure évaluation des risques associés aux fluctuations des taux d'intérêt dans différentes devises. La modification de la note pour exclure les expositions du secteur Services bancaires de gros clarifie également la portée des mesures de sensibilité, ce qui est crucial pour une évaluation précise des risques. Point de surveillance : Surveiller l'impact de cette nouvelle granularité sur la gestion des risques de taux d'intérêt et la manière dont elle pourrait influencer les décisions stratégiques de couverture de la banque.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1908,17 +1924,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
+          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1928,18 +1944,22 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt.</t>
+        </is>
+      </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+          <t>N’inclut pas les expositions du secteur Services bancaires de gros.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Hypothèses ou explications de risque Ce qui change : TD modifie la présentation des mesures de sensibilité au risque de taux d'intérêt structurel en ajoutant des notes qui précisent que les mesures seront présentées par devise à partir du 31 juillet 2025 et en modifiant la description des expositions incluses. Pertinence métier : Ce changement met en évidence une approche plus détaillée et granulaire de la gestion du risque de taux d'intérêt en introduisant une présentation par devise. Cela améliore la transparence et permet une meilleure évaluation des risques associés aux fluctuations des taux d'intérêt dans différentes devises. La modification de la note pour exclure les expositions du secteur Services bancaires de gros clarifie également la portée des mesures de sensibilité, ce qui est crucial pour une évaluation précise des risques. Point de surveillance : Surveiller l'impact de cette nouvelle granularité sur la gestion des risques de taux d'intérêt et la manière dont elle pourrait influencer les décisions stratégiques de couverture de la banque.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1964,7 +1984,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1979,18 +1999,18 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Obligations du gouvernement du Canada</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Autres titres de créance</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2015,7 +2035,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2030,18 +2050,18 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Autres titres</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2066,7 +2086,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2076,23 +2096,23 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Obligations du gouvernement des États-Unis</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2117,7 +2137,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2137,13 +2157,13 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
+          <t>Obligations du gouvernement du Canada</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2168,7 +2188,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2188,13 +2208,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement</t>
+          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2219,7 +2239,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2239,13 +2259,13 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Obligations de sociétés émettrices</t>
+          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Les indicateurs 'Autres titres de créance' et 'Autres titres' ont été ajoutés, tandis que plusieurs catégories d'obligations spécifiques ont été supprimées du tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE'. Une note a été ajoutée pour préciser que les titres comprennent ceux adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation. Pertinence métier : Ce changement met en évidence une réorganisation significative de la classification des actifs liquides, ce qui peut affecter la manière dont la banque gère et rapporte sa liquidité. La suppression des catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent indiquer un changement dans la stratégie de gestion des actifs liquides ou une réponse à des exigences réglementaires. Cela pourrait également avoir un impact sur la comparabilité des rapports entre les périodes et avec d'autres banques. Point de surveillance : Surveiller comment cette nouvelle classification des actifs liquides affecte les ratios de liquidité et la conformité aux exigences réglementaires, ainsi que l'impact potentiel sur la stratégie de gestion des risques de liquidité de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2265,7 +2285,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2275,7 +2295,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2285,18 +2305,18 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Autres titres de créance</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Obligations de sociétés émettrices</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2316,7 +2336,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2326,7 +2346,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2336,18 +2356,18 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Autres titres</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Obligations du gouvernement des États-Unis</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2367,7 +2387,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2377,28 +2397,28 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2418,7 +2438,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2428,7 +2448,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2443,13 +2463,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Obligations du gouvernement du Canada</t>
+          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE' en ajoutant les indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la présentation des actifs liquides, ce qui peut affecter la transparence et la comparabilité des informations sur la liquidité. En regroupant plusieurs catégories d'obligations sous des termes plus généraux, la banque pourrait simplifier la communication de ses actifs liquides, mais cela pourrait aussi réduire la granularité des informations disponibles pour les analystes et les régulateurs. Cette modification pourrait influencer la perception de la gestion de la liquidité de la banque par les parties prenantes. Point de surveillance : Surveiller l'impact de cette réorganisation sur la transparence des informations de liquidité et la réaction des régulateurs et des investisseurs.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2474,7 +2494,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2489,18 +2509,18 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Autres titres de créance</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2525,7 +2545,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -2540,18 +2560,18 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Autres titres</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2576,7 +2596,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2586,23 +2606,23 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Obligations du gouvernement des États-Unis</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2627,7 +2647,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2647,13 +2667,13 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
+          <t>Obligations du gouvernement du Canada</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2678,7 +2698,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2698,13 +2718,13 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement</t>
+          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : Le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' a été modifié avec l'ajout des indicateurs 'Autres titres de créance' et 'Autres titres', et la suppression de plusieurs catégories d'obligations spécifiques. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont la banque catégorise et présente ses actifs liquides. L'ajout de catégories plus générales et la suppression de catégories spécifiques peuvent indiquer un changement dans la stratégie de gestion de la liquidité ou une simplification de la présentation des actifs. Cela pourrait affecter la comparabilité avec les rapports précédents et entre pairs, et pourrait refléter une adaptation aux nouvelles attentes réglementaires ou aux conditions de marché. Point de surveillance : Surveiller l'impact de cette réorganisation sur la gestion de la liquidité et la conformité aux exigences réglementaires, ainsi que sur la transparence et la comparabilité des rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2724,17 +2744,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2744,18 +2764,18 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Dépôts personnels</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : Les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis' ont été remplacés par 'Dépôts personnels' et 'Dépôts non personnels'. La note associée a été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une modification de la méthodologie de calcul des dépôts, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement entre les pairs. La simplification des catégories de dépôts pourrait refléter une nouvelle approche de gestion du financement par la banque, influençant la transparence et la clarté des rapports financiers. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les rapports futurs et la manière dont elle pourrait affecter l'analyse des dépôts par les investisseurs et les régulateurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2775,17 +2795,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2795,18 +2815,18 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Dépôts non personnels</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Obligations de sociétés émettrices</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : Les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis' ont été remplacés par 'Dépôts personnels' et 'Dépôts non personnels'. La note associée a été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une modification de la méthodologie de calcul des dépôts, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement entre les pairs. La simplification des catégories de dépôts pourrait refléter une nouvelle approche de gestion du financement par la banque, influençant la transparence et la clarté des rapports financiers. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les rapports futurs et la manière dont elle pourrait affecter l'analyse des dépôts par les investisseurs et les régulateurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2826,42 +2846,38 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Les dépôts personnels et commerciaux aux États-Unis sont présentés selon un équivalent en dollars canadiens, par conséquent les variations d’une période à l’autre reflètent la croissance sous-jacente et les variations du taux de change.</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts mobilisés par l'entremise des services bancaires personnels et commerciaux et des activités de gestion de patrimoine.</t>
-        </is>
-      </c>
+          <t>Obligations du gouvernement des États-Unis</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : Les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis' ont été remplacés par 'Dépôts personnels' et 'Dépôts non personnels'. La note associée a été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une modification de la méthodologie de calcul des dépôts, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement entre les pairs. La simplification des catégories de dépôts pourrait refléter une nouvelle approche de gestion du financement par la banque, influençant la transparence et la clarté des rapports financiers. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les rapports futurs et la manière dont elle pourrait affecter l'analyse des dépôts par les investisseurs et les régulateurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2881,17 +2897,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2906,13 +2922,13 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Dépôts personnels et commerciaux – au Canada</t>
+          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : Les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis' ont été remplacés par 'Dépôts personnels' et 'Dépôts non personnels'. La note associée a été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une modification de la méthodologie de calcul des dépôts, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement entre les pairs. La simplification des catégories de dépôts pourrait refléter une nouvelle approche de gestion du financement par la banque, influençant la transparence et la clarté des rapports financiers. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les rapports futurs et la manière dont elle pourrait affecter l'analyse des dépôts par les investisseurs et les régulateurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2932,17 +2948,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2957,13 +2973,13 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Dépôts personnels et commerciaux – aux États-Unis¹</t>
+          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : Les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis' ont été remplacés par 'Dépôts personnels' et 'Dépôts non personnels'. La note associée a été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une modification de la méthodologie de calcul des dépôts, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement entre les pairs. La simplification des catégories de dépôts pourrait refléter une nouvelle approche de gestion du financement par la banque, influençant la transparence et la clarté des rapports financiers. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les rapports futurs et la manière dont elle pourrait affecter l'analyse des dépôts par les investisseurs et les régulateurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD modifie le tableau 'SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE' en ajoutant des indicateurs 'Autres titres de créance' et 'Autres titres', tout en supprimant plusieurs catégories spécifiques d'obligations. Pertinence métier : Ce changement met en évidence une réorganisation significative de la manière dont TD présente ses actifs liquides, ce qui pourrait refléter une modification de la stratégie de gestion de la liquidité ou une réponse à des exigences réglementaires. La suppression de catégories spécifiques d'obligations et l'ajout de catégories plus générales peuvent affecter la transparence et la comparabilité des actifs liquides de la banque, influençant ainsi la perception des investisseurs et des régulateurs sur la qualité et la liquidité des actifs détenus. Point de surveillance : Surveiller l'impact de cette réorganisation sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2978,47 +2994,43 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils, pour atteindre un maximum de 4,5 %. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 % pour atteindre un maximum de 4,5 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
+          <t>Dépôts personnels</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Fonds propres réglementaires Ce qui change : Les indicateurs 'Situation des fonds propres et ratios des fonds propres' et 'Fonds propres de catégories 1 et 2' ont été supprimés du tableau de gestion du capital. Pertinence métier : Ce changement met en évidence une modification significative dans la présentation des informations sur les fonds propres réglementaires. La suppression de ces indicateurs peut affecter la transparence et la comparabilité des informations sur les fonds propres entre les banques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller comment la banque communique désormais sur ses fonds propres et s'assurer que les exigences réglementaires en matière de divulgation sont toujours respectées.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Liquidité Ce qui change : TD modifie le tableau 'SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS' en ajoutant les indicateurs 'Dépôts personnels' et 'Dépôts non personnels', tout en supprimant les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis'. La note de bas de page a également été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une révision de la méthodologie de calcul des dépôts, ce qui peut avoir un impact sur la manière dont la banque évalue et gère sa liquidité. En modifiant les catégories de dépôts et la méthode de calcul, TD pourrait améliorer la précision de ses rapports de liquidité et sa capacité à répondre aux exigences réglementaires. Cela pourrait également affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les ratios de liquidité et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3033,22 +3045,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3058,18 +3070,18 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Situation des fonds propres et ratios des fonds propres</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Dépôts non personnels</t>
+        </is>
+      </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Fonds propres réglementaires Ce qui change : Les indicateurs 'Situation des fonds propres et ratios des fonds propres' et 'Fonds propres de catégories 1 et 2' ont été supprimés du tableau de gestion du capital. Pertinence métier : Ce changement met en évidence une modification significative dans la présentation des informations sur les fonds propres réglementaires. La suppression de ces indicateurs peut affecter la transparence et la comparabilité des informations sur les fonds propres entre les banques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller comment la banque communique désormais sur ses fonds propres et s'assurer que les exigences réglementaires en matière de divulgation sont toujours respectées.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Liquidité Ce qui change : TD modifie le tableau 'SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS' en ajoutant les indicateurs 'Dépôts personnels' et 'Dépôts non personnels', tout en supprimant les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis'. La note de bas de page a également été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une révision de la méthodologie de calcul des dépôts, ce qui peut avoir un impact sur la manière dont la banque évalue et gère sa liquidité. En modifiant les catégories de dépôts et la méthode de calcul, TD pourrait améliorer la précision de ses rapports de liquidité et sa capacité à répondre aux exigences réglementaires. Cela pourrait également affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les ratios de liquidité et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3084,43 +3096,47 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Fonds propres de catégories 1 et 2</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
+          <t>¹ Les dépôts personnels et commerciaux aux États-Unis sont présentés selon un équivalent en dollars canadiens, par conséquent les variations d’une période à l’autre reflètent la croissance sous-jacente et les variations du taux de change.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>¹ La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts mobilisés par l'entremise des services bancaires personnels et commerciaux et des activités de gestion de patrimoine.</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Fonds propres réglementaires Ce qui change : Les indicateurs 'Situation des fonds propres et ratios des fonds propres' et 'Fonds propres de catégories 1 et 2' ont été supprimés du tableau de gestion du capital. Pertinence métier : Ce changement met en évidence une modification significative dans la présentation des informations sur les fonds propres réglementaires. La suppression de ces indicateurs peut affecter la transparence et la comparabilité des informations sur les fonds propres entre les banques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller comment la banque communique désormais sur ses fonds propres et s'assurer que les exigences réglementaires en matière de divulgation sont toujours respectées.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Liquidité Ce qui change : TD modifie le tableau 'SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS' en ajoutant les indicateurs 'Dépôts personnels' et 'Dépôts non personnels', tout en supprimant les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis'. La note de bas de page a également été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une révision de la méthodologie de calcul des dépôts, ce qui peut avoir un impact sur la manière dont la banque évalue et gère sa liquidité. En modifiant les catégories de dépôts et la méthode de calcul, TD pourrait améliorer la précision de ses rapports de liquidité et sa capacité à répondre aux exigences réglementaires. Cela pourrait également affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les ratios de liquidité et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -3135,22 +3151,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3160,18 +3176,18 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Billets avec remboursement de capital à recours limité – série 6</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Dépôts personnels et commerciaux – au Canada</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Billets avec remboursement de capital à recours limité – série 6' et 'Évolution future des fonds propres réglementaires'. Suppression de la note sur le rachat des actions privilégiées. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure des fonds propres réglementaires de la banque, en introduisant de nouveaux instruments financiers et en supprimant des actions privilégiées. Cela reflète une stratégie potentielle de gestion du capital qui pourrait affecter la composition des fonds propres réglementaires et la capacité de la banque à répondre aux exigences prudentielles. Point de surveillance : Surveiller l'impact de ces nouveaux instruments sur les ratios de fonds propres réglementaires et la stratégie de capitalisation de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Liquidité Ce qui change : TD modifie le tableau 'SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS' en ajoutant les indicateurs 'Dépôts personnels' et 'Dépôts non personnels', tout en supprimant les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis'. La note de bas de page a également été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une révision de la méthodologie de calcul des dépôts, ce qui peut avoir un impact sur la manière dont la banque évalue et gère sa liquidité. En modifiant les catégories de dépôts et la méthode de calcul, TD pourrait améliorer la précision de ses rapports de liquidité et sa capacité à répondre aux exigences réglementaires. Cela pourrait également affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les ratios de liquidité et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3186,43 +3202,43 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>Pour les BRCRL, série 3, série 4 et série 6, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Dépôts personnels et commerciaux – aux États-Unis¹</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Billets avec remboursement de capital à recours limité – série 6' et 'Évolution future des fonds propres réglementaires'. Suppression de la note sur le rachat des actions privilégiées. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure des fonds propres réglementaires de la banque, en introduisant de nouveaux instruments financiers et en supprimant des actions privilégiées. Cela reflète une stratégie potentielle de gestion du capital qui pourrait affecter la composition des fonds propres réglementaires et la capacité de la banque à répondre aux exigences prudentielles. Point de surveillance : Surveiller l'impact de ces nouveaux instruments sur les ratios de fonds propres réglementaires et la stratégie de capitalisation de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Liquidité Ce qui change : TD modifie le tableau 'SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS' en ajoutant les indicateurs 'Dépôts personnels' et 'Dépôts non personnels', tout en supprimant les indicateurs 'Dépôts personnels et commerciaux – au Canada' et 'Dépôts personnels et commerciaux – aux États-Unis'. La note de bas de page a également été modifiée pour indiquer un changement dans la méthode de calcul. Pertinence métier : Ce changement met en évidence une révision de la méthodologie de calcul des dépôts, ce qui peut avoir un impact sur la manière dont la banque évalue et gère sa liquidité. En modifiant les catégories de dépôts et la méthode de calcul, TD pourrait améliorer la précision de ses rapports de liquidité et sa capacité à répondre aux exigences réglementaires. Cela pourrait également affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de cette nouvelle méthodologie sur les ratios de liquidité et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3242,17 +3258,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3262,23 +3278,27 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Le 30 avril 2024, la Banque a racheté la totalité de ses 14 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 22 (« actions privilégiées de série 22 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 22, pour un coût de rachat total de 350 millions de dollars.</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
+          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils, pour atteindre un maximum de 4,5 %. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 % pour atteindre un maximum de 4,5 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Billets avec remboursement de capital à recours limité – série 6' et 'Évolution future des fonds propres réglementaires'. Suppression de la note sur le rachat des actions privilégiées. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure des fonds propres réglementaires de la banque, en introduisant de nouveaux instruments financiers et en supprimant des actions privilégiées. Cela reflète une stratégie potentielle de gestion du capital qui pourrait affecter la composition des fonds propres réglementaires et la capacité de la banque à répondre aux exigences prudentielles. Point de surveillance : Surveiller l'impact de ces nouveaux instruments sur les ratios de fonds propres réglementaires et la stratégie de capitalisation de la banque.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Aucun changement substantiel Ce qui change : TD ne modifie pas le contenu ou la substance du tableau, mais seulement une reformulation sans impact sur le fond. Pertinence métier : Ce changement ne modifie pas la substance de la divulgation, car il s'agit d'une reformulation sans impact sur les risques, la gouvernance ou les exigences réglementaires. Il n'affecte pas la transparence ou la comparabilité des informations fournies par la banque. Point de surveillance : Aucun point de surveillance à retenir, car le changement est purement cosmétique.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr"/>
@@ -3293,17 +3313,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3319,12 +3339,12 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Ajustements de valorisation prudentiels</t>
+          <t>Billets avec remboursement de capital à recours limité – série 6</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : L'indicateur 'Ajustements de valorisation prudentiels' a été ajouté, tandis que 'Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme' a été supprimé dans le tableau 'STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III'. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque gère et présente ses ajustements de fonds propres sous Bâle III. L'ajout d'un indicateur sur les ajustements de valorisation prudentiels peut refléter une nouvelle approche ou une mise à jour des exigences réglementaires, ce qui est crucial pour la transparence et la conformité aux normes prudentielles. Point de surveillance : Surveiller comment ces ajustements de valorisation prudentiels influencent les ratios de fonds propres et si cela affecte la comparabilité avec les pairs ou les attentes réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -3344,38 +3364,38 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme d’actions ordinaires</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Pour les BRCRL, série 3, série 4 et série 6, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : L'indicateur 'Ajustements de valorisation prudentiels' a été ajouté, tandis que 'Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme' a été supprimé dans le tableau 'STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III'. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque gère et présente ses ajustements de fonds propres sous Bâle III. L'ajout d'un indicateur sur les ajustements de valorisation prudentiels peut refléter une nouvelle approche ou une mise à jour des exigences réglementaires, ce qui est crucial pour la transparence et la conformité aux normes prudentielles. Point de surveillance : Surveiller comment ces ajustements de valorisation prudentiels influencent les ratios de fonds propres et si cela affecte la comparabilité avec les pairs ou les attentes réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -3388,377 +3408,365 @@
       <c r="M56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Pour les BRCRL, série 3 et série 4, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Pour les BRCRL, série 3, série 4 et série 6, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Les soldes au 31 octobre 2023 ont été retraités, sans incidence sur l’évaluation des instruments financiers correspondants dans les états financiers consolidés de 2024 de la Banque, pour tenir compte du classement de certains actifs affectés en garantie dans la période comparative.</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : Le tableau 'ACTIFS GREVÉS ET ACTIFS NON GREVÉS' a été modifié avec l'ajout de l'indicateur 'Trésorerie et montants à recevoir de banques' et la suppression de 'Trésorerie et montants à recevoir'. De plus, une note a été supprimée et une autre modifiée. Pertinence métier : Ce changement met en évidence une réorganisation des indicateurs financiers dans le tableau, ce qui peut affecter la comparabilité des données entre les périodes et potentiellement influencer l'analyse de la liquidité et de la gestion des actifs de la banque. La suppression de la note sur le retraitement des soldes pourrait également avoir des implications sur la transparence des informations fournies. Point de surveillance : Surveiller l'impact de ces modifications sur la compréhension des actifs grevés et non grevés, ainsi que sur la transparence des informations financières fournies par la banque.</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>FINANCEMENT DE GROS</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Série 3</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Série 22</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Série 24</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>La présentation a été modifiée pour n’inclure que les dépôts commerciaux à échéance déterminée auprès de banques, afin de mieux harmoniser l’information avec la façon dont la direction perçoit la composition du financement de gros de la Banque.</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau 'FINANCEMENT DE GROS' a été modifié pour inclure des notes sur la dette de premier rang et les dépôts à échéance déterminée d'institutions autres que des banques, avec une mise à jour du montant de 26,9 milliards de dollars. Pertinence métier : Ce changement met en évidence une révision de la présentation des sources de financement de gros, ce qui peut affecter la perception de la liquidité et de la stabilité financière de la banque. L'ajout de détails sur la dette de premier rang et les dépôts non garantis est crucial pour évaluer la résilience en cas de crise, conformément aux attentes réglementaires sur la transparence des sources de financement. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de liquidité et la conformité aux exigences réglementaires en matière de financement de gros.</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Le 30 avril 2024, la Banque a racheté la totalité de ses 14 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 22 (« actions privilégiées de série 22 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 22, pour un coût de rachat total de 350 millions de dollars.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Structure du rapport Ce qui change : TD modifie le tableau 'ACTIONS ET AUTRES TITRES' en ajoutant l'indicateur 'Billets avec remboursement de capital à recours limité – série 6' et en supprimant les séries 3, 22 et 24. Pertinence métier : Ce changement met l'accent sur l'évolution de la structure du capital de la banque, en particulier avec l'ajout de nouveaux instruments financiers comme les billets avec remboursement de capital à recours limité (BRCRL) série 6. Cela reflète une stratégie potentielle de gestion du capital visant à optimiser la composition des fonds propres réglementaires. La suppression des séries 3, 22 et 24 pourrait indiquer un recentrage sur des instruments plus adaptés aux exigences actuelles du marché et de la réglementation. Cette modification affecte la transparence et la comparabilité des fonds propres de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion du capital de TD.</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du rapport de gestion du quatrième trimestre de 2025 de la Banque pour obtenir plus de renseignements.</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Hypothèses ou explications de risque Ce qui change : Une note a été ajoutée au tableau 'RATIO DE LIQUIDITÉ À COURT TERME MOYEN' précisant que les attentes de la Banque en matière de niveaux de liquidités reposent sur ses propres hypothèses. Pertinence métier : Ce changement met en évidence l'importance des hypothèses internes de la Banque dans la gestion de sa liquidité à court terme. Cela peut influencer la manière dont la Banque évalue ses besoins en liquidités et sa capacité à répondre aux exigences réglementaires. Les hypothèses sous-jacentes peuvent affecter la comparabilité avec d'autres banques qui pourraient utiliser des hypothèses différentes. Point de surveillance : Surveiller comment ces hypothèses influencent les niveaux de liquidité déclarés et si elles sont alignées avec les attentes réglementaires et les meilleures pratiques du secteur.</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>RATIO DE LIQUIDITÉ À LONG TERME¹</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Le NSFR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB.</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Nouvelle mention réglementaire Ce qui change : Ajout de notes précisant que le NSFR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, avec des détails sur les pondérations et les éléments interdépendants. Pertinence métier : Ce changement met en évidence l'alignement de la banque avec les normes de liquidité du BSIF, ce qui est crucial pour assurer la conformité réglementaire et la gestion efficace des risques de liquidité. La mention explicite des pondérations et des éléments interdépendants souligne l'application rigoureuse des normes, renforçant ainsi la transparence et la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité aux exigences du BSIF.</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-30T05:52:33.698573+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>RATIO DE LIQUIDITÉ À LONG TERME¹</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Les éléments présentés sous la catégorie « Aucune échéance » ne sont assortis d’aucune échéance précise. Cette catégorie regroupe notamment les fonds propres sans échéance, les dépôts sans échéance, les positions courtes, les positions à échéance ouverte, les actions qui ne remplissent pas les critères définissant les HQLA et les marchandises physiques.</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Nouvelle mention réglementaire Ce qui change : Ajout de notes précisant que le NSFR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, avec des détails sur les pondérations et les éléments interdépendants. Pertinence métier : Ce changement met en évidence l'alignement de la banque avec les normes de liquidité du BSIF, ce qui est crucial pour assurer la conformité réglementaire et la gestion efficace des risques de liquidité. La mention explicite des pondérations et des éléments interdépendants souligne l'application rigoureuse des normes, renforçant ainsi la transparence et la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité aux exigences du BSIF.</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-30T05:52:34.255830+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>RATIO DE LIQUIDITÉ À LONG TERME¹</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Les valeurs pondérées sont calculées après l’application des pondérations aux fins du NSFR prescrites par la ligne directrice Normes de liquidité du BSIF.</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Nouvelle mention réglementaire Ce qui change : Ajout de notes précisant que le NSFR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, avec des détails sur les pondérations et les éléments interdépendants. Pertinence métier : Ce changement met en évidence l'alignement de la banque avec les normes de liquidité du BSIF, ce qui est crucial pour assurer la conformité réglementaire et la gestion efficace des risques de liquidité. La mention explicite des pondérations et des éléments interdépendants souligne l'application rigoureuse des normes, renforçant ainsi la transparence et la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité aux exigences du BSIF.</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Ajustements de valorisation prudentiels</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : TD modifie la structure des fonds propres en ajoutant les 'Ajustements de valorisation prudentiels' et en supprimant les 'Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme'. Pertinence métier : Ce changement met en évidence une révision de la manière dont TD évalue et ajuste ses fonds propres réglementaires, ce qui peut avoir un impact sur la transparence et la comparabilité des fonds propres avec les exigences de Bâle III. L'ajout des ajustements de valorisation prudentiels pourrait indiquer une approche plus rigoureuse dans l'évaluation des actifs, tandis que la suppression des ajustements réglementaires précédents pourrait refléter une mise à jour des pratiques de conformité aux normes actuelles. Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de fonds propres et la conformité aux exigences de Bâle III.</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>RATIO DE LIQUIDITÉ À LONG TERME¹</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Certains éléments de l’actif et du passif réputés interdépendants par le BSIF, et à ce titre, leurs coefficients de FSR et de FSD sont ajustés à zéro. Les passifs interdépendants ne peuvent être échus pendant que l’actif demeure au bilan, ne peuvent servir à financer d’autres actifs tandis que le principal de l’actif ne peut servir qu’à rembourser le passif. Par conséquent, les seuls actifs et passifs interdépendants de la Banque qui sont admissibles à ce traitement sont les passifs découlant du Programme des Obligations hypothécaires du Canada et leurs actifs non grevés correspondants.</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Nouvelle mention réglementaire Ce qui change : Ajout de notes précisant que le NSFR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, avec des détails sur les pondérations et les éléments interdépendants. Pertinence métier : Ce changement met en évidence l'alignement de la banque avec les normes de liquidité du BSIF, ce qui est crucial pour assurer la conformité réglementaire et la gestion efficace des risques de liquidité. La mention explicite des pondérations et des éléments interdépendants souligne l'application rigoureuse des normes, renforçant ainsi la transparence et la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité aux exigences du BSIF.</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURE DES FONDS PROPRES ET RATIOS – Bâle III</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme d’actions ordinaires</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : TD modifie la structure des fonds propres en ajoutant les 'Ajustements de valorisation prudentiels' et en supprimant les 'Ajustements réglementaires appliqués aux fonds propres de catégorie 1 sous forme'. Pertinence métier : Ce changement met en évidence une révision de la manière dont TD évalue et ajuste ses fonds propres réglementaires, ce qui peut avoir un impact sur la transparence et la comparabilité des fonds propres avec les exigences de Bâle III. L'ajout des ajustements de valorisation prudentiels pourrait indiquer une approche plus rigoureuse dans l'évaluation des actifs, tandis que la suppression des ajustements réglementaires précédents pourrait refléter une mise à jour des pratiques de conformité aux normes actuelles. Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de fonds propres et la conformité aux exigences de Bâle III.</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3768,17 +3776,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
+          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3788,18 +3796,18 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>Comprend les expositions aux autres devises.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Les soldes au 31 octobre 2023 ont été retraités, sans incidence sur l’évaluation des instruments financiers correspondants dans les états financiers consolidés de 2024 de la Banque, pour tenir compte du classement de certains actifs affectés en garantie dans la période comparative.</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : Les notes du tableau sur la sensibilité au risque de taux d'intérêt structurel ont été modifiées pour inclure des précisions sur la présentation par devise et l'exclusion des expositions du secteur Services bancaires de gros. Pertinence métier : Ce changement met en évidence une approche plus détaillée et segmentée de la gestion du risque de taux d'intérêt, en alignement avec les attentes de transparence et de précision dans les rapports financiers. La présentation par devise permet une meilleure compréhension des expositions spécifiques, ce qui est crucial pour les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de cette segmentation sur la gestion des risques et la communication financière, ainsi que l'adaptation des systèmes de reporting pour intégrer ces nouvelles exigences.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : TD modifie le tableau des ACTIFS GREVÉS ET ACTIFS NON GREVÉS en supprimant des notes concernant le retraitement des soldes au 31 octobre 2023. Pertinence métier : Ce changement met en évidence une modification dans la structure du rapport de gestion de la banque, ce qui peut affecter la transparence et la compréhension des actifs grevés et non grevés. La suppression des notes pourrait réduire la clarté sur les retraitements effectués, ce qui est crucial pour les investisseurs et les régulateurs qui évaluent la qualité des actifs et la gestion des risques de la banque. Cela peut également influencer la comparabilité des rapports financiers avec ceux des périodes précédentes. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des informations financières et la perception des risques associés aux actifs grevés.</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -3814,22 +3822,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>ACTIFS PONDÉRÉS EN FONCTION DES RISQUES</t>
+          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3839,18 +3847,18 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>L’augmentation des actifs pondérés en fonction du risque opérationnel est attribuable essentiellement aux charges relatives à la résolution globale des enquêtes sur le programme de LCBA-BSA aux États-Unis de la Banque ainsi qu’à la croissance des activités.</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 31 octobre 2025 représente la moyenne des 62 données quotidiennes du trimestre.</t>
+        </is>
+      </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : La note expliquant l'augmentation des actifs pondérés en fonction du risque opérationnel a été supprimée. Cette note précisait que l'augmentation était essentiellement attribuable aux charges relatives. Pertinence métier : Ce changement met en évidence une modification dans la divulgation des facteurs influençant les actifs pondérés en fonction des risques. La suppression de cette note peut indiquer un changement dans la manière dont la banque communique sur ses risques opérationnels, ce qui est crucial pour comprendre les variations des actifs pondérés et leur impact sur le capital réglementaire. Point de surveillance : Surveiller les futures divulgations pour voir si la banque fournit des explications alternatives ou si elle modifie sa méthodologie de calcul des actifs pondérés en fonction des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires Ce qui change : TD modifie le tableau du RATIO DE LIQUIDITÉ À COURT TERME MOYEN en ajoutant des notes sur le calcul du LCR conformément à la ligne directrice Normes de liquidité du BSIF. Pertinence métier : Ce changement met l'accent sur la conformité de TD avec les exigences réglementaires en matière de liquidité, en précisant le calcul du LCR selon les normes du BSIF. Cela améliore la transparence et la comparabilité des pratiques de gestion de la liquidité de la banque avec celles de ses pairs, tout en renforçant la confiance des parties prenantes dans sa capacité à gérer les risques de liquidité. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité réglementaire de TD.</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -3870,7 +3878,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3878,22 +3886,30 @@
           <t>120</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Ajout</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Les valeurs non pondérées des entrées et des sorties de trésorerie représentent les soldes impayés qui arrivent à échéance ou qui deviennent exigibles dans les 30 jours.</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Le tableau contenant les indicateurs 'Total des entrées de trésorerie', 'Total des actifs liquides de haute qualité', 'Total des sorties nettes de trésorerie', et 'Ratio de liquidité à court terme' a été supprimé. Pertinence métier : Ce changement met en évidence une modification significative dans la divulgation des informations de liquidité. La suppression de ce tableau peut affecter la transparence et la capacité des parties prenantes à évaluer la position de liquidité de la banque. Les indicateurs de liquidité sont cruciaux pour comprendre la gestion des risques de liquidité et la conformité aux exigences réglementaires. Point de surveillance : Surveiller si cette suppression est compensée par une autre forme de divulgation ou si elle reflète un changement dans la stratégie de communication de la banque concernant sa liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires Ce qui change : TD modifie le tableau du RATIO DE LIQUIDITÉ À COURT TERME MOYEN en ajoutant des notes sur le calcul du LCR conformément à la ligne directrice Normes de liquidité du BSIF. Pertinence métier : Ce changement met l'accent sur la conformité de TD avec les exigences réglementaires en matière de liquidité, en précisant le calcul du LCR selon les normes du BSIF. Cela améliore la transparence et la comparabilité des pratiques de gestion de la liquidité de la banque avec celles de ses pairs, tout en renforçant la confiance des parties prenantes dans sa capacité à gérer les risques de liquidité. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité réglementaire de TD.</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -3905,8 +3921,298 @@
       <c r="L66" s="4" t="inlineStr"/>
       <c r="M66" s="4" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Les valeurs pondérées sont calculées après l’application des décotes des HQLA ou des taux des entrées et des sorties de trésorerie, et des plafonds prescrits par la ligne directrice Normes de liquidité du BSIF.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires Ce qui change : TD modifie le tableau du RATIO DE LIQUIDITÉ À COURT TERME MOYEN en ajoutant des notes sur le calcul du LCR conformément à la ligne directrice Normes de liquidité du BSIF. Pertinence métier : Ce changement met l'accent sur la conformité de TD avec les exigences réglementaires en matière de liquidité, en précisant le calcul du LCR selon les normes du BSIF. Cela améliore la transparence et la comparabilité des pratiques de gestion de la liquidité de la banque avec celles de ses pairs, tout en renforçant la confiance des parties prenantes dans sa capacité à gérer les risques de liquidité. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité réglementaire de TD.</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Sans objet conformément au modèle de divulgation commun du LCR.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires Ce qui change : TD modifie le tableau du RATIO DE LIQUIDITÉ À COURT TERME MOYEN en ajoutant des notes sur le calcul du LCR conformément à la ligne directrice Normes de liquidité du BSIF. Pertinence métier : Ce changement met l'accent sur la conformité de TD avec les exigences réglementaires en matière de liquidité, en précisant le calcul du LCR selon les normes du BSIF. Cela améliore la transparence et la comparabilité des pratiques de gestion de la liquidité de la banque avec celles de ses pairs, tout en renforçant la confiance des parties prenantes dans sa capacité à gérer les risques de liquidité. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité réglementaire de TD.</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>RATIO DE LIQUIDITÉ À COURT TERME MOYEN¹</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du rapport annuel 2024 de la Banque.</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Exigences réglementaires Ce qui change : TD modifie le tableau du RATIO DE LIQUIDITÉ À COURT TERME MOYEN en ajoutant des notes sur le calcul du LCR conformément à la ligne directrice Normes de liquidité du BSIF. Pertinence métier : Ce changement met l'accent sur la conformité de TD avec les exigences réglementaires en matière de liquidité, en précisant le calcul du LCR selon les normes du BSIF. Cela améliore la transparence et la comparabilité des pratiques de gestion de la liquidité de la banque avec celles de ses pairs, tout en renforçant la confiance des parties prenantes dans sa capacité à gérer les risques de liquidité. Point de surveillance : Surveiller l'impact de ces précisions sur la gestion de la liquidité et la conformité réglementaire de TD.</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>ACTIFS PONDÉRÉS EN FONCTION DES RISQUES</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>L’augmentation des actifs pondérés en fonction du risque opérationnel est attribuable essentiellement aux charges relatives à la résolution globale des enquêtes sur le programme de LCBA-BSA aux États-Unis de la Banque ainsi qu’à la croissance des activités.</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Capital réglementaire Ce qui change : TD modifie le tableau des ACTIFS PONDÉRÉS EN FONCTION DES RISQUES en supprimant une note expliquant l'augmentation des actifs pondérés en fonction du risque opérationnel. Pertinence métier : Ce changement met en évidence une modification dans la transparence des explications fournies sur les variations des actifs pondérés en fonction des risques. La suppression de la note peut affecter la compréhension des facteurs sous-jacents influençant le capital réglementaire, ce qui est crucial pour évaluer la résilience de la banque face aux risques opérationnels. Cela peut également avoir un impact sur la comparabilité des divulgations de la banque par rapport à ses pairs. Point de surveillance : Surveiller l'impact de cette suppression sur la clarté des informations fournies aux investisseurs et aux régulateurs concernant les risques opérationnels.</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Structure du rapport Ce qui change : TD supprime un tableau contenant des indicateurs clés de liquidité tels que le Total des entrées de trésorerie, Total des actifs liquides de haute qualité, Total des sorties nettes de trésorerie, et le Ratio de liquidité à court terme. Pertinence métier : Ce changement met en évidence une modification significative dans la divulgation des informations de liquidité de la banque. La suppression de ce tableau pourrait affecter la transparence et la capacité des parties prenantes à évaluer la position de liquidité de la banque. Cela pourrait également avoir un impact sur la comparabilité avec les pairs, car ces indicateurs sont cruciaux pour évaluer la résilience de la banque face aux chocs de liquidité. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des rapports de liquidité et la conformité aux exigences réglementaires en matière de divulgation.</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité, Ratio ou seuil prudentiel Ce qui change : TD supprime un tableau contenant des indicateurs clés de liquidité, notamment le Total du financement stable disponible, le Total du financement stable requis et le Ratio de liquidité à long terme. Pertinence métier : Ce changement met en évidence une modification significative dans la divulgation des informations de liquidité de la banque. La suppression de ce tableau peut affecter la transparence et la capacité des parties prenantes à évaluer la gestion de la liquidité à long terme de TD. Cela pourrait également influencer la perception de la conformité de la banque avec les exigences réglementaires en matière de liquidité, notamment les ratios de financement stable. La comparabilité avec les pairs pourrait être affectée si ces indicateurs ne sont plus disponibles. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des informations de liquidité et la conformité aux exigences réglementaires.</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M66"/>
+  <autoFilter ref="A1:M72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>